--- a/Pamodzi Covid-19 Study/data/Study site.xlsx
+++ b/Pamodzi Covid-19 Study/data/Study site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Desktop\Git R project\R_Projects\Pamodzi Covid-19 Study\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3BCFBC62-5A5C-4531-A7E1-9AE678B66872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550F6524-424F-4AD4-A0A1-1FCC5BD3420D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{D0C4DCB1-3C93-40FD-B153-DDA090CBABBE}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{D0C4DCB1-3C93-40FD-B153-DDA090CBABBE}"/>
   </bookViews>
   <sheets>
     <sheet name="mwi_admbnda_adm2_nso_hotosm_202" sheetId="1" r:id="rId1"/>
@@ -127,10 +127,10 @@
     <t>study status</t>
   </si>
   <si>
-    <t>Study site</t>
-  </si>
-  <si>
     <t>Not Study site</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Study site</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -1043,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -1093,7 +1093,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -1133,7 +1133,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
@@ -1153,7 +1153,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -1163,7 +1163,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -1173,7 +1173,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -1193,7 +1193,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -1203,7 +1203,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1253,7 +1253,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -1263,7 +1263,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1273,7 +1273,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1283,7 +1283,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -1293,7 +1293,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1303,7 +1303,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
